--- a/docs/官方数据与算法来源.xlsx
+++ b/docs/官方数据与算法来源.xlsx
@@ -1,29 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\卫星仿真平台\docs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DBEC909-F546-4F3F-89B5-9691EEAB2FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="20" windowWidth="25540" windowHeight="15260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="60" yWindow="20" windowWidth="25540" windowHeight="15260"/>
   </bookViews>
   <sheets>
-    <sheet name="官方数据与算法来源" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="官方数据与算法来源" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">官方数据与算法来源!$A$1:$H$21</definedName>
+    <definedName name="_xlnm._FilterDatabase">'官方数据与算法来源'!$A$1:$H$13,'官方数据与算法来源'!$A$19:$H$26</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="160">
   <si>
     <t>序号</t>
   </si>
@@ -157,6 +151,9 @@
     <t>packages/core/utils/constants.js（P838_TABLE）</t>
   </si>
   <si>
+    <t>官方值与插值混合</t>
+  </si>
+  <si>
     <t>地形海拔</t>
   </si>
   <si>
@@ -172,6 +169,9 @@
     <t>resources/itu/topo_v1.bin · packages/core/utils/elevation.js</t>
   </si>
   <si>
+    <t>采用 5 弧分采样（2164×4324），非最细 1 弧分</t>
+  </si>
+  <si>
     <t>地形高度框架</t>
   </si>
   <si>
@@ -250,16 +250,106 @@
     <t>Natural Earth（NACIS，公有领域）</t>
   </si>
   <si>
-    <t>由北美制图信息协会(NACIS)支持、众多制图师志愿维护的公有领域(public domain)矢量与栅格地图数据集，提供 1:10m / 1:50m / 1:110m 多尺度国界、海岸线、行政区等，无版权限制、广泛用于专业制图。本平台经 TopoJSON world-atlas 封装使用。</t>
+    <t>由北美制图信息协会(NACIS)支持、众多制图师志愿维护的公有领域(public domain)矢量与栅格地图数据集，提供 1:10m / 1:50m / 1:110m 多尺度国界、海岸线、行政区等，无版权限制、广泛用于专业制图。本平台主底图由 scripts/build-basemap.mjs 直接从 NE shapefile 构建成「争议单元级的面 + 归属映射表」，国界与着色在运行时按视角解算。</t>
   </si>
   <si>
     <t>底图边界</t>
   </si>
   <si>
-    <t>src/viz/globe3d/data/countries-10m|50m|110m.json · china-provinces.json</t>
-  </si>
-  <si>
-    <t>多尺度矢量边界</t>
+    <t>scripts/build-basemap.mjs → src/viz/globe3d/data/basemap-{10m,50m,110m}.json · 视角表 src/viz/geo/povs/*.json · 解算器 src/viz/geo/povResolver.js · 消费 src/viz/flatmap/flatCoverage.js 与 src/viz/globe3d/scene.js；旧的 TopoJSON world-atlas 封装 countries-50m.json 仅剩链路预算地理场图 src/shared/lbBasemap.js 在用</t>
+  </si>
+  <si>
+    <t>NE 5.1.1（boundary_lines_land 5.1.0），三档量化 1e5 ≈ 0.0036°/格；50m/110m 经 backfill-basemap.mjs 回填粗档缺失单元</t>
+  </si>
+  <si>
+    <t>行政区界（一级）</t>
+  </si>
+  <si>
+    <t>Natural Earth 10m Admin 1 – States, Provinces（NACIS，公有领域）</t>
+  </si>
+  <si>
+    <t>由北美制图信息协会(NACIS)支持维护的公有领域(public domain)矢量数据集中的一级行政区图层，1:10m 精度、4596 个单元，带 name_en / name_zh 等多语名称列。本平台 251 个国家/地区的省级界线均出自此层，版本 5.1.1。</t>
+  </si>
+  <si>
+    <t>一级行政区界与地名</t>
+  </si>
+  <si>
+    <t>scripts/build-adm.mjs → resources/adm/{ISO3}-adm1.json（251 份）· 索引与署名 src/viz/globe3d/data/adm/{index,ATTRIBUTION}.json · 消费 electron/services/admBoundaries.js → src/viz/geo/admPacks.js</t>
+  </si>
+  <si>
+    <t>NE 5.1.1 原生精度；只保留被两个单元共享的边，坐标量化 3 位小数（≈110 m）、DP 抽稀 0.003°</t>
+  </si>
+  <si>
+    <t>行政区界（中国两级）</t>
+  </si>
+  <si>
+    <t>阿里云 DataV.GeoAtlas areas_v3（数据源：中华人民共和国民政部行政区划）</t>
+  </si>
+  <si>
+    <t>阿里云 DataV.GeoAtlas 公共服务提供的中国行政区划边界接口，数据源为民政部行政区划。中国两级不用 NE / geoBoundaries：NE 的 CHN admin_1 只有 32 个（台港澳被当作独立 admin_0），geoBoundaries 的 CHN ADM2 是县级 2391 个且全为拼音；DataV 的疆域口径（台港澳、藏南、阿克赛钦）与本平台红线一致，且省界市界出自同一套几何。</t>
+  </si>
+  <si>
+    <t>中国省界 / 地级市界与地名</t>
+  </si>
+  <si>
+    <t>scripts/lib/chinaDatav.mjs · scripts/build-adm.mjs → resources/adm/CHN-adm1.json（34 省）· CHN-adm2.json（332 地级市）</t>
+  </si>
+  <si>
+    <t>民政部口径原生精度；对外正式出版的地图仍须换用带审图号的底图</t>
+  </si>
+  <si>
+    <t>行政区界（二级 · 备用源）</t>
+  </si>
+  <si>
+    <t>geoBoundaries gbOpen（wmgeolab，逐国 CC BY 4.0 / ODbL / PDDL）</t>
+  </si>
+  <si>
+    <t>由威廉玛丽学院 geoLab 维护的全球行政边界开放数据库，gbOpen 版逐国给出 ADM0–ADM2 边界与各自的开放许可。构建脚本 build-adm.mjs 支持从它出别国的二级行政区。★ 截至 2026-09-05 仓库中一份 gbOpen 产物都没有——ADM2 只出了中国一份且走 DataV，故当前无逐国许可需署名。</t>
+  </si>
+  <si>
+    <t>别国二级行政区界（当前未启用）</t>
+  </si>
+  <si>
+    <t>scripts/build-adm.mjs（GB_META = geoBoundariesOpen-meta.csv）· 缓存 scripts/_ne/gb-*.zip</t>
+  </si>
+  <si>
+    <t>未随包分发；启用后逐国许可写入 ATTRIBUTION.json</t>
+  </si>
+  <si>
+    <t>真彩影像底图</t>
+  </si>
+  <si>
+    <t>NASA Visible Earth · Blue Marble Next Generation（world.topo.bathy.200407，公有领域）</t>
+  </si>
+  <si>
+    <t>NASA 地球观测站(Earth Observatory)发布的全球真彩合成影像，topo+bathy 版带真实地形晕渲与水深晕渲，2004 年 7 月合成（12 月版北半球雪线偏南，不适合做通用底图）。八分幅版 21600×21600×8 = 500 m/px，单张版 21600×10800 = 1.86 km/px。使用时署名 NASA Earth Observatory。</t>
+  </si>
+  <si>
+    <t>3D 球体 / 2D 平面图的影像底图</t>
+  </si>
+  <si>
+    <t>scripts/build-imagery-tiles.mjs → resources/imagery/bmng（L0–L6，4273 片 / 100 MB，不进 git）· 整幅档 src/viz/globe3d/textures/{16k,8k}_earth_bmng.jpg · 消费 src/viz/imageryTiles.js · src/viz/imagery.js</t>
+  </si>
+  <si>
+    <t>瓦片档 L6 = 978 m/px（EPSG:4326 / GIBS 网格，512² 片 + 1 px gutter）；整幅档 16384×8192 = 2.45 km/px，受 GPU 纹理上限封死。发版自检 npm run check:imagery</t>
+  </si>
+  <si>
+    <t>地图注记表（手写）</t>
+  </si>
+  <si>
+    <t>GB/T 2659《世界各国和地区名称代码》· 各条注记逐点可查</t>
+  </si>
+  <si>
+    <t>三张本平台手写的注记表：国名中文名与 ISO 数字码按 GB/T 2659 通行简称；水域注记 77 条取各水域的开阔水面（不取质心，质心会落到陆地上）；岛链 3 条按通行定义逐岛列出 123 个可查锚点、在经纬度平面加密到 1°。国名标注锚点原取自 NE 10m map_units 的 LABEL_X/LABEL_Y，2026-09-05 起对三条落海的（GNQ / NZL / TTO）由本平台覆写。</t>
+  </si>
+  <si>
+    <t>国名 / 水域名 / 岛链参考线</t>
+  </si>
+  <si>
+    <t>src/viz/geo/countryZh.js（268 条，174 条带锚点）· waterNames.js（77 条）· islandChains.js（3 条 / 123 锚点）</t>
+  </si>
+  <si>
+    <t>不变量由 packages/core/test/mapAnnotations.test.mjs 与 mapGeometry.test.mjs 逐点守住（落水 / 落岛 / 落本国单元、加密间距）</t>
   </si>
   <si>
     <t>大地坐标基准</t>
@@ -407,53 +497,38 @@
   </si>
   <si>
     <t>格式权威；数值来自运营商</t>
-  </si>
-  <si>
-    <t>官方值与插值混合</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>采用 5 弧分采样（2164×4324），非最细 1 弧分</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <charset val="134"/>
+      <family val="2"/>
       <sz val="11"/>
       <name val="Microsoft YaHei"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <family val="2"/>
+      <sz val="10"/>
+      <name val="Microsoft YaHei"/>
     </font>
     <font>
+      <charset val="134"/>
+      <family val="2"/>
       <sz val="10"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -493,24 +568,24 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -806,9 +881,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr defaultRowHeight="14" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -820,555 +895,684 @@
     <col min="8" max="8" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="95" customHeight="1">
-      <c r="A2" s="1">
+    <row r="2" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="95" customHeight="1">
-      <c r="A3" s="1">
+    <row r="3" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="95" customHeight="1">
-      <c r="A4" s="1">
+    <row r="4" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="95" customHeight="1">
-      <c r="A5" s="1">
+    <row r="5" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="B5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="95" customHeight="1">
-      <c r="A6" s="1">
+    <row r="6" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="B6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="95" customHeight="1">
-      <c r="A7" s="1">
+    <row r="7" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="B7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>43</v>
       </c>
       <c r="H7" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="95" customHeight="1">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" s="4" t="s">
+      <c r="H21" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="95" customHeight="1">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="95" customHeight="1">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="95" customHeight="1">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="95" customHeight="1">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="95" customHeight="1">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="95" customHeight="1">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="95" customHeight="1">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="95" customHeight="1">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="95" customHeight="1">
-      <c r="A17" s="1">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="95" customHeight="1">
-      <c r="A18" s="1">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="95" customHeight="1">
-      <c r="A19" s="1">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="95" customHeight="1">
-      <c r="A20" s="1">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D20" s="2" t="s">
+    <row r="22" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="95" customHeight="1">
-      <c r="A21" s="1">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>127</v>
+      <c r="C22" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="23" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="25" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="26" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H21" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <autoFilter ref="A1:H21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/官方数据与算法来源.xlsx
+++ b/docs/官方数据与算法来源.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="191">
   <si>
     <t>序号</t>
   </si>
@@ -497,6 +497,99 @@
   </si>
   <si>
     <t>格式权威；数值来自运营商</t>
+  </si>
+  <si>
+    <t>厂家公开资料</t>
+  </si>
+  <si>
+    <t>CnC PSD 比窗口</t>
+  </si>
+  <si>
+    <t>Comtech EF Data · CDM-625A Advanced Satellite Modem 数据表（DoubleTalk Carrier-in-Carrier 节）</t>
+  </si>
+  <si>
+    <t>Comtech EF Data 是卫星调制解调器主要厂家之一，DoubleTalk Carrier-in-Carrier 是其载波叠加实现。数据表给出收端两载波功率谱密度比的允许区间：BPSK/QPSK/8PSK/8-QAM 为 −7～+11 dB，16-QAM 为 −7～+7 dB。32-ary 数据表未给窗，本平台按 ±7 dB 处理（与 16-QAM 同档，偏保守），更高阶无厂家窗、只告警。</t>
+  </si>
+  <si>
+    <t>「高级计算 · CNC 载波叠加」的 PSD 比窗口校验</t>
+  </si>
+  <si>
+    <t>src/shared/advBalance.js（CNC_MOD_SPEC）</t>
+  </si>
+  <si>
+    <t>厂家数据表原值；两端可在对话框手填覆盖</t>
+  </si>
+  <si>
+    <t>CnC 固有处理损耗 deg₀</t>
+  </si>
+  <si>
+    <t>Comtech EF Data · CDM-625A 数据表（同上）</t>
+  </si>
+  <si>
+    <t>同一份数据表给出 PSD 比为 0 dB 时的 Eb/N₀ 退化：BPSK/QPSK/OQPSK 0.3 dB、8-QAM 0.4 dB、8PSK 0.5 dB、16-QAM 0.6 dB、32-ary 0.6 dB。这是调制解调器抵消处理本身的代价，与抵消深度无关——抵消再深也去不掉这一截。★ 与 CDM-Qx 手册 §9 算例给的「总退化 −0.1 / 0.0 dB」互相矛盾（总退化不可能小于固有损耗），本平台按数据表建模并在测试 ⑭ 的注释里写明这处矛盾。</t>
+  </si>
+  <si>
+    <t>并联进载波带内 C/I，折成 C/(N+I) 退化</t>
+  </si>
+  <si>
+    <t>src/shared/advBalance.js（CNC_MOD_SPEC · solveCnc）</t>
+  </si>
+  <si>
+    <t>厂家数据表原值；可在对话框手填覆盖（置 0 即只算抵消残余）</t>
+  </si>
+  <si>
+    <t>CnC 抵消深度 D（缺省 28 dB）</t>
+  </si>
+  <si>
+    <t>Comtech EF Data · CDM-Qx Installation and Operation Manual, Chapter 9（非对称算例 Table 9-2）</t>
+  </si>
+  <si>
+    <t>数据表不给抵消深度。本平台按 CDM-Qx 手册 §9 的非对称算例反推：QPSK 3/4（目标 C/N ≈ 6.3 dB）在 PSD 比 ±5.3 dB 处，抵消残余项须压到 0.05 dB 以内才与算例相符 ⇒ D ≥ 28 dB。取 28 作缺省。★ 这是反推值不是厂家标称值，实测抵消深度应按设备填。</t>
+  </si>
+  <si>
+    <t>残余自干扰 C/I = D − PSD 比</t>
+  </si>
+  <si>
+    <t>src/shared/advBalance.js（CNC_DEFAULTS.cancelDb）</t>
+  </si>
+  <si>
+    <t>反推值；测试 ⑭ 核对「抵消残余项 @ D=28 ≤ 0.2 dB」</t>
+  </si>
+  <si>
+    <t>CnC 符号率比上限 / 最小符号率 / 时延窗</t>
+  </si>
+  <si>
+    <t>Comtech EF Data · CDM-Qx 手册 Chapter 9（CnC）</t>
+  </si>
+  <si>
+    <t>手册 §9 给出：非对称速率比至 3（TX:RX 或 RX:TX）、最小符号率 128 ksps、CnC 比通常小于 10 dB、卫星时延窗 0–330 ms（典型 230–270 ms）。前两项做成可改参数并在越界时告警（能算、不拦下）；时延窗不作输入——GEO 单跳回环恒在窗内，只在界面 title 注明。</t>
+  </si>
+  <si>
+    <t>符号率比与最小符号率校验</t>
+  </si>
+  <si>
+    <t>src/shared/advBalance.js（CNC_DEFAULTS · solveCnc 的告警段）</t>
+  </si>
+  <si>
+    <t>厂家手册原值；均可在对话框手填覆盖</t>
+  </si>
+  <si>
+    <t>CnC 拓扑约束与 CnC-APC</t>
+  </si>
+  <si>
+    <t>ViaSat PCMA（Paired Carrier Multiple Access）公开资料；Comtech CDM-625A 数据表（CnC-APC 节）；美国专利 US 8,849,193 / US 8,634,778</t>
+  </si>
+  <si>
+    <t>PCMA 是载波叠加的原始实现。拓扑上要求前向与返向在同一转发器、构成一对双工、各站必须收得到自己的上行回波（否则无从抵消）——本平台据此新增「双工配对」校验。CnC-APC：两端自动测量并补偿上行雨衰、维持总合成功率，本平台只实现「PSD 比被保持」这一层语义（区间坍缩到晴空），不做功率再分配算法。UPC 补偿范围据 PCMA 资料约 3 dB。</t>
+  </si>
+  <si>
+    <t>双工配对校验 · CnC-APC 开关</t>
+  </si>
+  <si>
+    <t>src/shared/advBalance.js（validateCnc · solveCnc 的 apc 分支）</t>
+  </si>
+  <si>
+    <t>仅实现「ρ 被保持」语义；功率再分配未做</t>
   </si>
 </sst>
 </file>
@@ -882,7 +975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="14" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1571,6 +1664,136 @@
         <v>159</v>
       </c>
     </row>
+    <row r="27" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="28" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="29" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="30" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="31" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/官方数据与算法来源.xlsx
+++ b/docs/官方数据与算法来源.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="214">
   <si>
     <t>序号</t>
   </si>
@@ -590,6 +590,75 @@
   </si>
   <si>
     <t>仅实现「ρ 被保持」语义；功率再分配未做</t>
+  </si>
+  <si>
+    <t>年 → 最坏月换算</t>
+  </si>
+  <si>
+    <t>ITU-R Recommendation P.841-6</t>
+  </si>
+  <si>
+    <t>ITU-R《年统计量与最坏月统计量的换算》建议书。全球模型给出 p_w = (p / Q₁)^(1/β)，全球平均取 Q₁ = 0.30、β = 1.15：年平均超越时间百分比 p 换算为最坏月的超越百分比 p_w。年 99.8 % 折成最坏月 99.297 %，年 99.9 % 折成 99.615 %。</t>
+  </si>
+  <si>
+    <t>SLA「按月考核」档的可用度折算（与雨衰页同式）</t>
+  </si>
+  <si>
+    <t>src/shared/lbSla.js（worstMonthAvail）· packages/core/utils/rainAttenuation.js:291</t>
+  </si>
+  <si>
+    <t>建议书原式；测试 ⑩ 钉住六个换算值（±1e-3）</t>
+  </si>
+  <si>
+    <t>准无误码（QEF）门限与 FECFRAME 长度</t>
+  </si>
+  <si>
+    <t>ETSI EN 302 307-1 / EN 302 307-2（DVB-S2 / S2X）</t>
+  </si>
+  <si>
+    <t>欧洲电信标准化协会(ETSI)的数字卫星广播第二代标准。§4.1 把解调门限定义在准无误码(QEF)点上，约合传输包错误率 PER &lt; 10⁻⁷；正常 FECFRAME 长 64800 bit，一帧净荷 ≈ 64800 × FEC 码率。</t>
+  </si>
+  <si>
+    <t>丢包率的帧差错模型：p = 1 − (1 − FER)^N_f，N_f = ⌈8L / K⌉</t>
+  </si>
+  <si>
+    <t>src/shared/lbSla.js（frameLossPct · framesPerPacket · DVB_FECFRAME_BITS）</t>
+  </si>
+  <si>
+    <t>标准原值；K 取正常 FECFRAME 的近似（未扣 BCH 冗余，误差 &lt; 0.5 %）</t>
+  </si>
+  <si>
+    <t>可用度指标口径</t>
+  </si>
+  <si>
+    <t>ITU-R Recommendation S.579-6</t>
+  </si>
+  <si>
+    <t>ITU-R《固定卫星业务假想参考电路与假想参考数字链路的可用度目标》建议书。给出 FSS 链路可用度的定义与目标口径（不可用状态的判据、统计周期）。</t>
+  </si>
+  <si>
+    <t>SLA 报告「系统可用度」条款的口径基准</t>
+  </si>
+  <si>
+    <t>src/shared/lbSlaReport.js（DEFS.sysAvail · REFS.sla）</t>
+  </si>
+  <si>
+    <t>仅作口径引用；本平台不套用其具体目标数值</t>
+  </si>
+  <si>
+    <t>误码性能指标口径</t>
+  </si>
+  <si>
+    <t>ITU-R Recommendation S.1062-4</t>
+  </si>
+  <si>
+    <t>ITU-R《固定卫星业务假想参考数字链路的允许误码性能》建议书。给出数字链路误码性能指标的定义与统计口径（误块秒、严重误块秒等）。</t>
+  </si>
+  <si>
+    <t>SLA 报告「设计误码率 / 丢包率上限」条款的口径基准</t>
+  </si>
+  <si>
+    <t>src/shared/lbSlaReport.js（DEFS.berTarget · DEFS.loss · REFS.sla）</t>
   </si>
 </sst>
 </file>
@@ -975,7 +1044,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="14" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1794,6 +1863,110 @@
         <v>190</v>
       </c>
     </row>
+    <row r="32" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="33" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="34" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="35" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/官方数据与算法来源.xlsx
+++ b/docs/官方数据与算法来源.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="289">
   <si>
     <t>序号</t>
   </si>
@@ -499,6 +499,195 @@
     <t>格式权威；数值来自运营商</t>
   </si>
   <si>
+    <t>NR MCS 表与 TBS 算法</t>
+  </si>
+  <si>
+    <t>3GPP TS 38.214 V17.4.0 §5.1.3.1 / §5.1.3.2 / §6.1.4.1</t>
+  </si>
+  <si>
+    <t>3GPP《NR 物理层数据处理规程》技术规范。Table 5.1.3.1-1/-2/-3 给出 PDSCH/PUSCH 的三张 MCS 表（调制阶数 Qm 与目标码率 R），Table 6.1.4.1-1/-2 给出变换预编码使能时 PUSCH 专用的两张表（只用于 PUSCH，PDSCH 没有这两张）；§5.1.3.2 与 Table 5.1.3.2-1 给出精确传输块大小算法（N′_RE 每 PRB 封顶 156、N_info 量化、3840/3816/8424 三支）。本平台 149 行 MCS 与 93 档量化表逐条转录自原文。</t>
+  </si>
+  <si>
+    <t>MODCOD 表 / 速率</t>
+  </si>
+  <si>
+    <t>packages/core/utils/constants.js（五张 NR 表）· packages/core/utils/ntnPhy.js（nrTbsPerSlot / TBS_QUANT）</t>
+  </si>
+  <si>
+    <t>逐值核对（V17.4.0）；变换预编码表已锁定为仅上行</t>
+  </si>
+  <si>
+    <t>SNR / SINR 的每 RE 定义</t>
+  </si>
+  <si>
+    <t>3GPP TS 38.215 §5.1.6（SS-SINR / CSI-SINR）</t>
+  </si>
+  <si>
+    <t>3GPP《NR 物理层测量》技术规范。§5.1.6 把 SINR 定义为「承载参考信号的各资源元素(RE)上信号功率的线性平均 ÷ 同一带宽内各 RE 上噪声与干扰功率的线性平均」，即【按资源元素定义】。UE 上报的 SINR、gNB 从 DMRS 估出的 PUSCH SNR、模组 AT 指令回的读数都是这一口径。本平台 3GPP 载波的解调门限口径(noiseRatioMode = snr)据此钉死：噪声带宽取占用带宽 N_RB×12×SCS（NB-IoT 上行为音数×SCS）。</t>
+  </si>
+  <si>
+    <t>解调门限口径</t>
+  </si>
+  <si>
+    <t>packages/core/utils/ntnPhy.js · packages/core/utils/linkCalculator.js</t>
+  </si>
+  <si>
+    <t>口径定义；平台不变式由 ntnSnrEngine.test.mjs 锁定</t>
+  </si>
+  <si>
+    <t>NR 数据速率近似式与开销系数</t>
+  </si>
+  <si>
+    <t>3GPP TS 38.306 §4.1.2</t>
+  </si>
+  <si>
+    <t>3GPP《NR 用户设备无线接入能力》技术规范。§4.1.2 给出峰值数据速率的近似式 R = ν·Qm·f·R·(N_RB·12/T_s)·(1−OH)，其中 T_s 为含循环前缀的平均符号时长、OH 为系统开销系数（FR1 下行 0.14 / 上行 0.08，FR2 下行 0.18 / 上行 0.10）。本平台把它作为 TBS 精确算法之外的第二种速率模型(rateModel = oh38306)，用于「整载波平均吞吐」这一类估算。</t>
+  </si>
+  <si>
+    <t>信息速率</t>
+  </si>
+  <si>
+    <t>packages/core/utils/ntnPhy.js（nrInfoRateKbps）</t>
+  </si>
+  <si>
+    <t>校验值 106 RB@15 kHz / 64QAM 948 / OH 0.14 → 85.07 Mbps</t>
+  </si>
+  <si>
+    <t>NR-NTN 频段、信道带宽档与资源块数</t>
+  </si>
+  <si>
+    <t>3GPP TS 38.101-5 V19.5.0 (2026-08) Table 5.2.2-1 / 5.2.3-1 / 5.3.2-1 / 5.3.2-2 / 5.3.5-1 / 5.3.5-2</t>
+  </si>
+  <si>
+    <t>3GPP《NR 卫星接入无线发送与接收》技术规范。Table 5.3.2-1/-2 给出各子载波间隔下「信道带宽 ↔ 最大资源块数 N_RB」（FR1 与 FR2 两张，同一个 60 kHz/50 MHz 分别是 65 与 66 RB，不可合并）；Table 5.3.5-1/-2 另给出【逐频段】允许的信道带宽档，两张表缺一不可 —— 只看前者会配出 5 MHz@30 kHz、n254 的 20 MHz 这类标准里不存在的载波。Table 5.2.2-1/5.2.3-1 给出各频段收发频率范围。本平台按 V19.5.0 全量收录 14 个频段（FR1 九个：n256/n255/n254/n253/n252/n251/n250 与 Ku 的 n248/n247；FR2 五个：n512/n511/n510 与 Ku 的 n509/n508），含「本版可选」与「仅下行」两类标注。★ 30 MHz 在三个版本的 Table 5.3.5-1 里都没有任何频段列出（CR 0033 只往 N_RB 表加了一列），故不作为可选档。</t>
+  </si>
+  <si>
+    <t>带宽档位</t>
+  </si>
+  <si>
+    <t>packages/core/utils/ntnPhy.js（NTN_BANDS / NR_RB_FR1 / NR_RB_FR2）· src/shared/ntnLimits.js</t>
+  </si>
+  <si>
+    <t>V19.5.0 逐值转录（含 FR2 的 Table 5.3.2-2，早先「按 38.101-2 同值收」的诚实边界已消解）</t>
+  </si>
+  <si>
+    <t>NB-IoT TBS 表与单音 MCS 映射</t>
+  </si>
+  <si>
+    <t>3GPP TS 36.213 V17.4.0 / V18.3.0 Table 16.4.1.5.1-1 · 16.5.1.2-1/-2 · 16.4.1.3-2 · 16.5.1.1-3</t>
+  </si>
+  <si>
+    <t>3GPP《E-UTRA 物理层规程》技术规范。Table 16.4.1.5.1-1 与 16.5.1.2-2 给出 NB-IoT 下行/上行的传输块大小表（行 I_TBS 0–13、列 I_SF/I_RU 0–7）；Table 16.5.1.2-1 给出 NPUSCH 单音的 I_MCS →（调制, I_TBS）映射（I_MCS 0/1 为 π/2-BPSK、2 起为 π/4-QPSK，且 1 与 2 的 I_TBS 是反的）；Table 16.4.1.3-2 / 16.5.1.1-3 给出重复次数枚举（NPDSCH 1…2048 共 16 档、NPUSCH 1…128 共 8 档）。§16.4.1.5.1 规定 NPDSCH 的 I_TBS 上限随部署模式变（带内 10、独立/保护带 13）。本平台已按 Rel-14 全表收录（Cat-NB2，IoT-NTN 商用模组的主流）。★ (I_TBS 13, I_SF/I_RU 3) 一格 V14.2.0 印 1128、V17.4.0/V18.3.0 印 1032，以新版为准。16QAM 档（Rel-17，I_TBS 14–21）未收。</t>
+  </si>
+  <si>
+    <t>NB-IoT 速率</t>
+  </si>
+  <si>
+    <t>packages/core/utils/ntnPhy.js（NB_TBS_DL / NB_TBS_UL / NB_ST_MCS / NB_NREP_*）</t>
+  </si>
+  <si>
+    <t>Rel-14 全表逐值转录；已用 Kodheli 表 3 的频谱效率列反推交叉验证（28 格中 25 格吻合到 1e-4）</t>
+  </si>
+  <si>
+    <t>NTN 链路预算 CNR 式与参考参数</t>
+  </si>
+  <si>
+    <t>3GPP TR 38.821 V16.2.0（NR-NTN）· TR 36.763 V17.0.0（IoT-NTN）</t>
+  </si>
+  <si>
+    <t>3GPP 关于非地面网络的两份技术报告。§6.1.3.1 给出 NTN 链路预算的载噪比式 CNR = EIRP + G/T − k − 各项路径损耗 − 10·lg(B)，其中 B 是【本次分配的带宽】（NR 下行取整载波系统带宽，上行手持终端取小分配；NB-IoT 下行 180 kHz、上行按音数取 3.75 / 15 / 45 / 90 / 180 kHz）。本平台 3GPP 载波的噪声带宽取法与此完全一致。</t>
+  </si>
+  <si>
+    <t>链路预算口径</t>
+  </si>
+  <si>
+    <t>packages/core/utils/ntnPhy.js（文件头口径推导）</t>
+  </si>
+  <si>
+    <t>口径依据</t>
+  </si>
+  <si>
+    <t>公开研究数据</t>
+  </si>
+  <si>
+    <t>NR 解调门限基线（主锚点）</t>
+  </si>
+  <si>
+    <t>Méndez-Monsanto 等《BLER-SNR Curves for 5G NR MCS under AWGN Channel with Optimum Quantization》, IEEE VTC2024-Fall</t>
+  </si>
+  <si>
+    <t>西班牙马德里卡洛斯三世大学(UC3M)与英国约克大学(University of York)合作、发表于 IEEE 车载技术会议(VTC2024-Fall)的链路级仿真研究。用 MATLAB 5G Toolbox 在 AWGN、SISO、大传输块(4.9k–61k bit)条件下逐 MCS 跑出 BLER-SNR 曲线（BLER 1e-2 至 1e-8）。本平台 NR 五张 MODCOD 表的门限列以其 BLER 1e-2 值减 0.3 dB 为主锚点，拟合出「Shannon 极限 + 按调制族线性变化的实现差距」模型后逐档生成。3GPP 本身不规定 MCS ↔ SNR 对照。</t>
+  </si>
+  <si>
+    <t>解调门限</t>
+  </si>
+  <si>
+    <t>packages/core/utils/constants.js（NR 五张表的门限列 + 拟合式注释）</t>
+  </si>
+  <si>
+    <t>AWGN / SISO / 大码块 / BLER 10% 首传；实际 NTN 信道另需 1–3 dB</t>
+  </si>
+  <si>
+    <t>NR 解调门限基线（次锚点）</t>
+  </si>
+  <si>
+    <t>《Fluid Antenna System Empowering 5G NR》表 II（arXiv 2503.05384）</t>
+  </si>
+  <si>
+    <t>公开预印本中给出的 CQI ↔ SNR 对照表：SISO、AWGN、5 MHz、线性拟合到 BLER 0.1（QPSK 78/1024 的 −7.84 dB 至 64QAM 948/1024 的 20.03 dB）。与上一条共同作为本平台 NR 门限拟合式的最小二乘锚点。</t>
+  </si>
+  <si>
+    <t>packages/core/utils/constants.js（拟合式注释）</t>
+  </si>
+  <si>
+    <t>BLER 0.1；作次锚点</t>
+  </si>
+  <si>
+    <t>NB-IoT 解调门限基线</t>
+  </si>
+  <si>
+    <t>Kodheli, Maturo, Andrenacci, Chatzinotas, Zimmer,《Link budget analysis for satellite-based narrowband IoT systems》, AdHoc-Now 2019</t>
+  </si>
+  <si>
+    <t>卢森堡大学 SnT 与合作方发表的卫星 NB-IoT 链路预算研究。表 3 给出 NPDSCH / NPUSCH 多音 / NPUSCH 单音在 AWGN、Turbo 码、N_rep = 1、每档取最大吞吐 TBS、BLER 10% 首传条件下的所需 SNR（SNR 定义在各自的分配带宽上）。本平台 NB-IoT 三张表的门限列逐值取自此表；2026-09-05 之前的旧预置比它乐观 0.3–3.0 dB。</t>
+  </si>
+  <si>
+    <t>packages/core/utils/constants.js（NB-IoT 三张表的门限列）</t>
+  </si>
+  <si>
+    <t>逐值转录；AWGN / BLER 10% 首传 / N_rep = 1</t>
+  </si>
+  <si>
+    <t>NR 门限参照（不作基线）</t>
+  </si>
+  <si>
+    <t>srsRAN Project · lib/scheduler/support/mcs_calculator.cpp 的 UL SNR→MCS 表</t>
+  </si>
+  <si>
+    <t>开源 5G 协议栈 srsRAN Project（西班牙 Software Radio Systems 公司主导）中真实 gNB 调度器用的上行 SNR→MCS 门限表，条件为 AWGN 信道(ZMQ 环回)、20 MHz SISO、判据「BLER = 0%」，作者在源码里自标 temporary。它是「厂家口径」的一个实例，与链路级仿真在 64QAM 高码率段可差 3 dB 以上，故本平台只在代码注释里列作参照，不作门限基线。</t>
+  </si>
+  <si>
+    <t>参照对比</t>
+  </si>
+  <si>
+    <t>packages/core/utils/constants.js（注释）</t>
+  </si>
+  <si>
+    <t>仅参照；判据与条件与本平台基线不同</t>
+  </si>
+  <si>
+    <t>5G-LENA（CTTC）· nr-eesm-t1.cc / nr-eesm-t2.cc</t>
+  </si>
+  <si>
+    <t>西班牙加泰罗尼亚电信技术中心(CTTC)维护的 ns-3 5G-LENA 模块中，按码块规模分表的 NR 合规链路级仿真门限。其 BLER 10% 绝对值比上述两份研究高 3–5 dB，故绝对值不采用；但其「小码块惩罚」（码块 ≤ 500 bit 比 ≥ 3000 bit 高 +0.3 至 +2.2 dB）可用作提示——NTN 上行 1–2 PRB 的小分配恰在此区间。本平台把它作为元数据写进悬停说明，不自动加到门限上。</t>
+  </si>
+  <si>
+    <t>packages/core/utils/constants.js（注释）· MODCOD 表悬停说明</t>
+  </si>
+  <si>
+    <t>仅参照；小码块惩罚不自动折算</t>
+  </si>
+  <si>
     <t>厂家公开资料</t>
   </si>
   <si>
@@ -659,6 +848,42 @@
   </si>
   <si>
     <t>src/shared/lbSlaReport.js（DEFS.berTarget · DEFS.loss · REFS.sla）</t>
+  </si>
+  <si>
+    <t>IoT-NTN 终端射频与信道带宽</t>
+  </si>
+  <si>
+    <t>3GPP TS 36.102 V18.11.0 (2026-02) Table 5.2-1 / 5.3A-1 / 5.3B-1 · §5.4B</t>
+  </si>
+  <si>
+    <t>3GPP《E-UTRA 卫星接入用户设备无线发送与接收》技术规范 —— IoT-NTN 终端侧的独立射频分册（SAN 侧对应 TS 36.108）。Table 5.3B-1：NB1/NB2 信道带宽 200 kHz、N_RB = 1、每 RU 子载波数 12@15 kHz / 48@3.75 kHz；Table 5.3A-1：Cat-M1 信道带宽 1.4 MHz、N_RB = 6；§5.4B.1：独立部署标称信道栅格 200 kHz、带内 180 kHz；Table 5.2-1：卫星接入 E-UTRA 频段 256/255/254/253（全 FDD，NB1/NB2 为 HD-FDD）。本平台早先注释里写「36.101 不分册、IoT-NTN 未见独立的 UE 射频分册」，那条诚实边界已由本规范消解。</t>
+  </si>
+  <si>
+    <t>NB-IoT 带宽限值</t>
+  </si>
+  <si>
+    <t>src/shared/ntnLimits.js（NTN_BW_LIMITS 的 ref 与 scope）</t>
+  </si>
+  <si>
+    <t>逐值核对（V18.11.0）；eMTC（Cat-M1）本平台未收，仅备注</t>
+  </si>
+  <si>
+    <t>NB-IoT 帧结构与资源单元（有效码率分母）</t>
+  </si>
+  <si>
+    <t>3GPP TS 36.211 V14.2.0 Table 10.1.2.3-1 · Table 10.1.4.2-1 · §10.2.3 · §10.2.6.2</t>
+  </si>
+  <si>
+    <t>3GPP《E-UTRA 物理信道与调制》技术规范。Table 10.1.2.3-1 给出 NPUSCH 格式 1 的（子载波间隔, 每 RU 子载波数, 时隙数, 每时隙符号数）——12/6/3 子载波各为 1/2/4 ms、单音 15 kHz 为 8 ms、3.75 kHz 为 32 ms；Table 10.1.4.2-1 给出每时隙 1 个 DMRS 符号；§10.2.3 定死 NPDSCH 一个 NB-IoT 载波 = 1 个 PRB = 12 子载波 × 15 kHz；§10.2.6.2 给出 NRS 的位置（每端口每子帧 8 RE，2 个端口时另一端口位置也不载数据）。本平台据此算出每传输块的编码比特数：NPDSCH 独立/保护带 304 bit、带内 208 bit，NPUSCH 多音 288 bit、单音 96×Qm bit —— 即 MODCOD 表「FEC 码率」列的分母。★ 早先这一列写成 TBS/264，264 对哪张表都不是分母。</t>
+  </si>
+  <si>
+    <t>NB-IoT 有效码率</t>
+  </si>
+  <si>
+    <t>packages/core/utils/ntnPhy.js（NB_CODED_BITS / nbCodeRate）· packages/core/utils/constants.js（三张 NB 表的 fec 列）</t>
+  </si>
+  <si>
+    <t>按原文结构逐项推算；三张表的分母与分子（含 24 bit CRC）已进单测</t>
   </si>
 </sst>
 </file>
@@ -1044,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr defaultRowHeight="14" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1738,25 +1963,25 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="F27" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="G27" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="H27" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="28" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1764,25 +1989,25 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="F28" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="G28" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="H28" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="29" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1790,25 +2015,25 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="F29" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="G29" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="H29" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="30" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1816,25 +2041,25 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="F30" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="G30" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="H30" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="31" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1842,25 +2067,25 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="G31" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="H31" s="3" t="s">
         <v>189</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="32" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1871,22 +2096,22 @@
         <v>117</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="E32" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="F32" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="G32" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="H32" s="3" t="s">
         <v>195</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="33" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1894,7 +2119,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>117</v>
+        <v>196</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>197</v>
@@ -1920,7 +2145,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>117</v>
+        <v>196</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>203</v>
@@ -1932,13 +2157,13 @@
         <v>205</v>
       </c>
       <c r="F34" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G34" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="H34" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="35" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1946,25 +2171,363 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="36" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="37" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="38" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="39" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="40" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="41" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="42" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="43" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>208</v>
+      <c r="C43" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="44" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="45" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="46" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="47" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="48" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>288</v>
       </c>
     </row>
   </sheetData>

--- a/docs/官方数据与算法来源.xlsx
+++ b/docs/官方数据与算法来源.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="258">
   <si>
     <t>序号</t>
   </si>
@@ -686,99 +686,6 @@
   </si>
   <si>
     <t>仅参照；小码块惩罚不自动折算</t>
-  </si>
-  <si>
-    <t>厂家公开资料</t>
-  </si>
-  <si>
-    <t>CnC PSD 比窗口</t>
-  </si>
-  <si>
-    <t>Comtech EF Data · CDM-625A Advanced Satellite Modem 数据表（DoubleTalk Carrier-in-Carrier 节）</t>
-  </si>
-  <si>
-    <t>Comtech EF Data 是卫星调制解调器主要厂家之一，DoubleTalk Carrier-in-Carrier 是其载波叠加实现。数据表给出收端两载波功率谱密度比的允许区间：BPSK/QPSK/8PSK/8-QAM 为 −7～+11 dB，16-QAM 为 −7～+7 dB。32-ary 数据表未给窗，本平台按 ±7 dB 处理（与 16-QAM 同档，偏保守），更高阶无厂家窗、只告警。</t>
-  </si>
-  <si>
-    <t>「高级计算 · CNC 载波叠加」的 PSD 比窗口校验</t>
-  </si>
-  <si>
-    <t>src/shared/advBalance.js（CNC_MOD_SPEC）</t>
-  </si>
-  <si>
-    <t>厂家数据表原值；两端可在对话框手填覆盖</t>
-  </si>
-  <si>
-    <t>CnC 固有处理损耗 deg₀</t>
-  </si>
-  <si>
-    <t>Comtech EF Data · CDM-625A 数据表（同上）</t>
-  </si>
-  <si>
-    <t>同一份数据表给出 PSD 比为 0 dB 时的 Eb/N₀ 退化：BPSK/QPSK/OQPSK 0.3 dB、8-QAM 0.4 dB、8PSK 0.5 dB、16-QAM 0.6 dB、32-ary 0.6 dB。这是调制解调器抵消处理本身的代价，与抵消深度无关——抵消再深也去不掉这一截。★ 与 CDM-Qx 手册 §9 算例给的「总退化 −0.1 / 0.0 dB」互相矛盾（总退化不可能小于固有损耗），本平台按数据表建模并在测试 ⑭ 的注释里写明这处矛盾。</t>
-  </si>
-  <si>
-    <t>并联进载波带内 C/I，折成 C/(N+I) 退化</t>
-  </si>
-  <si>
-    <t>src/shared/advBalance.js（CNC_MOD_SPEC · solveCnc）</t>
-  </si>
-  <si>
-    <t>厂家数据表原值；可在对话框手填覆盖（置 0 即只算抵消残余）</t>
-  </si>
-  <si>
-    <t>CnC 抵消深度 D（缺省 28 dB）</t>
-  </si>
-  <si>
-    <t>Comtech EF Data · CDM-Qx Installation and Operation Manual, Chapter 9（非对称算例 Table 9-2）</t>
-  </si>
-  <si>
-    <t>数据表不给抵消深度。本平台按 CDM-Qx 手册 §9 的非对称算例反推：QPSK 3/4（目标 C/N ≈ 6.3 dB）在 PSD 比 ±5.3 dB 处，抵消残余项须压到 0.05 dB 以内才与算例相符 ⇒ D ≥ 28 dB。取 28 作缺省。★ 这是反推值不是厂家标称值，实测抵消深度应按设备填。</t>
-  </si>
-  <si>
-    <t>残余自干扰 C/I = D − PSD 比</t>
-  </si>
-  <si>
-    <t>src/shared/advBalance.js（CNC_DEFAULTS.cancelDb）</t>
-  </si>
-  <si>
-    <t>反推值；测试 ⑭ 核对「抵消残余项 @ D=28 ≤ 0.2 dB」</t>
-  </si>
-  <si>
-    <t>CnC 符号率比上限 / 最小符号率 / 时延窗</t>
-  </si>
-  <si>
-    <t>Comtech EF Data · CDM-Qx 手册 Chapter 9（CnC）</t>
-  </si>
-  <si>
-    <t>手册 §9 给出：非对称速率比至 3（TX:RX 或 RX:TX）、最小符号率 128 ksps、CnC 比通常小于 10 dB、卫星时延窗 0–330 ms（典型 230–270 ms）。前两项做成可改参数并在越界时告警（能算、不拦下）；时延窗不作输入——GEO 单跳回环恒在窗内，只在界面 title 注明。</t>
-  </si>
-  <si>
-    <t>符号率比与最小符号率校验</t>
-  </si>
-  <si>
-    <t>src/shared/advBalance.js（CNC_DEFAULTS · solveCnc 的告警段）</t>
-  </si>
-  <si>
-    <t>厂家手册原值；均可在对话框手填覆盖</t>
-  </si>
-  <si>
-    <t>CnC 拓扑约束与 CnC-APC</t>
-  </si>
-  <si>
-    <t>ViaSat PCMA（Paired Carrier Multiple Access）公开资料；Comtech CDM-625A 数据表（CnC-APC 节）；美国专利 US 8,849,193 / US 8,634,778</t>
-  </si>
-  <si>
-    <t>PCMA 是载波叠加的原始实现。拓扑上要求前向与返向在同一转发器、构成一对双工、各站必须收得到自己的上行回波（否则无从抵消）——本平台据此新增「双工配对」校验。CnC-APC：两端自动测量并补偿上行雨衰、维持总合成功率，本平台只实现「PSD 比被保持」这一层语义（区间坍缩到晴空），不做功率再分配算法。UPC 补偿范围据 PCMA 资料约 3 dB。</t>
-  </si>
-  <si>
-    <t>双工配对校验 · CnC-APC 开关</t>
-  </si>
-  <si>
-    <t>src/shared/advBalance.js（validateCnc · solveCnc 的 apc 分支）</t>
-  </si>
-  <si>
-    <t>仅实现「ρ 被保持」语义；功率再分配未做</t>
   </si>
   <si>
     <t>年 → 最坏月换算</t>
@@ -1269,7 +1176,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultRowHeight="14" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -2249,25 +2156,25 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="D38" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="F38" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="G38" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="H38" s="3" t="s">
         <v>228</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="39" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2275,25 +2182,25 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>223</v>
+        <v>117</v>
       </c>
       <c r="C39" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="E39" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="F39" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="G39" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="H39" s="3" t="s">
         <v>234</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="40" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2301,25 +2208,25 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>223</v>
+        <v>117</v>
       </c>
       <c r="C40" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="E40" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="F40" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="G40" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="H40" s="3" t="s">
         <v>240</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="41" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2327,25 +2234,25 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>223</v>
+        <v>117</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="E41" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="F41" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="G41" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>246</v>
-      </c>
       <c r="H41" s="3" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
     </row>
     <row r="42" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2353,25 +2260,25 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>223</v>
+        <v>117</v>
       </c>
       <c r="C42" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="F42" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="G42" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="H42" s="3" t="s">
         <v>251</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="43" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2382,152 +2289,22 @@
         <v>117</v>
       </c>
       <c r="C43" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E43" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="F43" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="G43" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="H43" s="3" t="s">
         <v>257</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="44" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
-        <v>43</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="45" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
-        <v>44</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="46" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
-        <v>45</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="47" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
-        <v>46</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="48" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
-        <v>47</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>288</v>
       </c>
     </row>
   </sheetData>

--- a/docs/官方数据与算法来源.xlsx
+++ b/docs/官方数据与算法来源.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="282">
   <si>
     <t>序号</t>
   </si>
@@ -791,13 +791,85 @@
   </si>
   <si>
     <t>按原文结构逐项推算；三张表的分母与分子（含 24 bit CRC）已进单测</t>
+  </si>
+  <si>
+    <t>卫星编目 SATCAT</t>
+  </si>
+  <si>
+    <t>CelesTrak Satellite Catalog（satcat.csv，访问日期 2026-09-16）</t>
+  </si>
+  <si>
+    <t>CelesTrak（由 T.S. Kelso 博士维护）按美国空间监视网（SSN）公开编目整理的全部空间目标清单，每日一版。17 列：名称 / 国际编号 / NORAD 号 / 对象类型 / 运行状态 / 所有者 / 发射日期 / 发射场 / 陨落日期 / 周期 / 倾角 / 远地点 / 近地点 / RCS / 数据状态 / 轨道中心 / 轨道类型。2026-09-16 实测 70,667 条、6,737,839 字节。★ 不用旧的定宽 satcat.txt —— 它只含 NORAD &lt; 70000，而编目号已用到 100691。</t>
+  </si>
+  <si>
+    <t>空间态势报告：编目总览 / 轨道区制 / 所有者 / 发射与陨落 / 大型星座部署</t>
+  </si>
+  <si>
+    <t>electron/services/omm.js（DATASETS.satcat）· packages/core/utils/satcatValid.js · src/shared/ssaStats.js</t>
+  </si>
+  <si>
+    <t>众包四级链路（当日缓存 → CelesTrak 直连 → 腾讯云 COS 镜像 → 旧缓存 / 内置快照）；随安装包内置 resources/omm/csv_satcat.csv.gz</t>
+  </si>
+  <si>
+    <t>所有者代码表</t>
+  </si>
+  <si>
+    <t>CelesTrak SATCAT Sources（satcat/sources.php，访问日期 2026-09-16）</t>
+  </si>
+  <si>
+    <t>SATCAT 的 OWNER 列代码表：国家、国际组织与运营商的 2–4 字母代码 → 全名。2026-09-16 实测 132 条。★ 上游未收录 JOR / KWT / SVK / UGA 四国（近年首次发星），已在生成脚本的 MANUAL_OWNER 里补齐；台港澳相关代码的名称按平台主权口径改写（中国台湾 / Taiwan, China）。</t>
+  </si>
+  <si>
+    <t>所有者代码 → 中英文名</t>
+  </si>
+  <si>
+    <t>scripts/build-satcat-codes.mjs → src/shared/satcatCodes.js（OWNER）</t>
+  </si>
+  <si>
+    <t>生成物提交进仓库，运行时不联网；satcatCodes.test.mjs 扫真实编目核验未命中为 0</t>
+  </si>
+  <si>
+    <t>发射场代码表</t>
+  </si>
+  <si>
+    <t>CelesTrak SATCAT Launch Sites（satcat/launchsites.php，访问日期 2026-09-16）</t>
+  </si>
+  <si>
+    <t>SATCAT 的 LAUNCH_SITE 列代码表：发射场 3–5 字母代码 → 名称与所在地。2026-09-16 实测 41 条，覆盖编目里出现的全部 37 个代码。</t>
+  </si>
+  <si>
+    <t>发射场代码 → 中英文名</t>
+  </si>
+  <si>
+    <t>scripts/build-satcat-codes.mjs → src/shared/satcatCodes.js（LAUNCH_SITE）</t>
+  </si>
+  <si>
+    <t>生成物提交进仓库；中文名为标准译名，人工翻译</t>
+  </si>
+  <si>
+    <t>运行状态与字段定义</t>
+  </si>
+  <si>
+    <t>CelesTrak SATCAT Status Codes / Format（satcat/status.php · satcat/satcat-format.php，访问日期 2026-09-16）</t>
+  </si>
+  <si>
+    <t>status.php 给出 OPS_STATUS_CODE 八档：+ 运行 / - 停运 / P 部分运行 / B 备份 / S 备用 / X 延寿 / D 已陨落 / ? 未知。satcat-format.php 给出 OBJECT_TYPE（PAY / R/B / DEB / UNK）、ORBIT_TYPE（ORB / LAN / IMP / DOC / R/T）、ORBIT_CENTER（EA 或其它天体 / 停靠母体 NORAD）、DATA_STATUS_CODE（NCE / NIE / NEA）及各数值列的量纲。</t>
+  </si>
+  <si>
+    <t>活跃载荷判据（+ P B S X）、在轨 / 已陨落 / 深空判据</t>
+  </si>
+  <si>
+    <t>src/shared/satcatCodes.js（OPS_STATUS / OBJECT_TYPE / ORBIT_TYPE / ORBIT_CENTER / DATA_STATUS · ACTIVE_STATUS）· src/shared/ssaStats.js</t>
+  </si>
+  <si>
+    <t>判据全文写进报告「口径与判据」一节；ssaStats.test.mjs 逐条断言</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -824,6 +896,7 @@
       <sz val="10"/>
       <name val="微软雅黑"/>
     </font>
+    <font/>
   </fonts>
   <fills count="2">
     <fill>
@@ -860,7 +933,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -874,6 +947,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1176,7 +1251,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultRowHeight="14" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -2281,7 +2356,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="43" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" ht="95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2306,6 +2381,114 @@
       <c r="H43" s="3" t="s">
         <v>257</v>
       </c>
+    </row>
+    <row r="44" ht="95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="5">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="I44" s="6"/>
+    </row>
+    <row r="45" ht="95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="5">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="I45" s="6"/>
+    </row>
+    <row r="46" ht="95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="5">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="I46" s="6"/>
+    </row>
+    <row r="47" ht="95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="5">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="I47" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H21"/>

--- a/docs/官方数据与算法来源.xlsx
+++ b/docs/官方数据与算法来源.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="305">
   <si>
     <t>序号</t>
   </si>
@@ -863,6 +863,75 @@
   </si>
   <si>
     <t>判据全文写进报告「口径与判据」一节；ssaStats.test.mjs 逐条断言</t>
+  </si>
+  <si>
+    <t>太阳射电流量（多频逐日）</t>
+  </si>
+  <si>
+    <t>野边山射电偏振计 NoRP 逐日总流量（国立天文台野边山太阳射电观测所，nsro/norp/data/daily/nbymYYMM，2004-10…2026-07，访问日期 2026-09-21）</t>
+  </si>
+  <si>
+    <t>日本国立天文台（NAOJ）野边山太阳电波观测所的射电偏振计，1 / 2 / 3.75 / 9.4 / 17 GHz 五个频点逐日测太阳全日面总流量（单位 sfu = 1e-22 W·m⁻²·Hz⁻¹），是公开的多频太阳射电长序列。35 / 80 GHz 两个频点的流量刻度按手册 man_v04e §2 固定为 2400 / 9000 sfu 的静日标定值。</t>
+  </si>
+  <si>
+    <t>太阳亮温谱（日凌）</t>
+  </si>
+  <si>
+    <t>docs/research/solar-flux-fit/norp/ · packages/core/utils/sunOutageCalculator.js（SOLAR_ANCHORS / S_Q_HIGH）</t>
+  </si>
+  <si>
+    <t>252 个月表入库；与 F10.7 配对 7 325 天，逐频回归系数为终值</t>
+  </si>
+  <si>
+    <t>太阳射电流量 F10.7（逐日观测）</t>
+  </si>
+  <si>
+    <t>DRAO Penticton F10.7 逐日表（加拿大自然资源部空间天气，spaceweather.gc.ca/solar_flux_data/daily_flux_values/fluxtable.txt，访问日期 2026-09-21）</t>
+  </si>
+  <si>
+    <t>加拿大彭蒂克顿 Dominion 射电天文台自 1947 年起连续测量的 10.7 cm（2.8 GHz）太阳射电流量，是 F10.7 指数的原始观测源，全球太阳活动的基准长序列。回归用 fluxobsflux（观测值）列的 20 UT 那次。</t>
+  </si>
+  <si>
+    <t>回归自变量（日凌太阳亮温）</t>
+  </si>
+  <si>
+    <t>docs/research/solar-flux-fit/fit.mjs（原始 2 MB 表未入库，README 有下载命令）</t>
+  </si>
+  <si>
+    <t>仅用于离线拟合；运行时不取这一路</t>
+  </si>
+  <si>
+    <t>F10.7 月均（观测 / 预测）</t>
+  </si>
+  <si>
+    <t>NOAA SWPC Solar Cycle Indices（services.swpc.noaa.gov/json/solar-cycle/observed-solar-cycle-indices.json · predicted-solar-cycle.json，访问日期 2026-09-21）</t>
+  </si>
+  <si>
+    <t>美国国家海洋和大气管理局空间天气预报中心（NOAA SWPC）发布的太阳周指数：观测月均（实测 F10.7 自 2004-10 起，更早的行为 -1）与太阳周预测月均（含 25/75 分位带，到 2030-12）。日凌按目标日落在过去 / 未来分别取这两条。</t>
+  </si>
+  <si>
+    <t>F10.7 按目标日期取值</t>
+  </si>
+  <si>
+    <t>electron/services/solarFlux.js · packages/core/utils/solarFluxPick.js · resources/space-weather/solar-flux.json</t>
+  </si>
+  <si>
+    <t>随安装包内置快照兜底；一天一次后台刷新，计算不等网络</t>
+  </si>
+  <si>
+    <t>F10.7 日值与短期预报</t>
+  </si>
+  <si>
+    <t>NOAA SWPC 10cm Flux 30-Day / 45-Day Forecast（services.swpc.noaa.gov/products/10cm-flux-30-day.json · text/45-day-forecast.txt，访问日期 2026-09-21）</t>
+  </si>
+  <si>
+    <t>NOAA SWPC 的短期产品：最近 30 天 20 UT 的 F10.7 观测日值，与未来 45 天的 F10.7 预报。日凌取分点日 ±20 天窗口内的均值，全是观测记「观测」、含预报记「45 天预报」。</t>
+  </si>
+  <si>
+    <t>electron/services/solarFlux.js · packages/core/utils/solarFluxPick.js（parseDaily30 / parseForecast45）</t>
+  </si>
+  <si>
+    <t>窗口内不足 10 天有值时自动落到月均那一档</t>
   </si>
 </sst>
 </file>
@@ -933,7 +1002,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -948,7 +1017,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1251,7 +1321,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultRowHeight="14" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -2356,7 +2426,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="43" ht="95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" ht="95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2489,6 +2559,110 @@
         <v>281</v>
       </c>
       <c r="I47" s="6"/>
+    </row>
+    <row r="48" ht="110" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="7">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="49" ht="90" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="7">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="50" ht="105" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="7">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="51" ht="90" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="7">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>304</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H21"/>
